--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.7428571428571429</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6619718309859155</v>
+        <v>0.647887323943662</v>
       </c>
       <c r="D2">
-        <v>0.48</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="E2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
